--- a/ImportSmallBatchForTest.xlsx
+++ b/ImportSmallBatchForTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB0C467D-D362-4EF2-8D4C-F2CD5FE12ECF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35AD7AE-0AA8-4EAF-ACF6-99E1C43252C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{543EC62A-26F7-482D-96ED-BF73340C8FC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="218" xr2:uid="{543EC62A-26F7-482D-96ED-BF73340C8FC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="182">
   <si>
     <t>Lead.City</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>Michael kfoury</t>
+  </si>
+  <si>
+    <t>ewerton.mattos@lumonpay.com</t>
   </si>
 </sst>
 </file>
@@ -1059,6 +1062,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C0C2139-B013-4871-B638-12EE72D68F02}">
   <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="25.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:90" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1353,7 +1360,7 @@
         <v>93</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>95</v>
@@ -1439,8 +1446,8 @@
       <c r="AP2" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ2" s="8" t="s">
-        <v>94</v>
+      <c r="AQ2" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR2" s="8"/>
       <c r="AS2" s="8" t="s">
@@ -1591,7 +1598,7 @@
         <v>93</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>95</v>
@@ -1679,8 +1686,8 @@
       <c r="AP3" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ3" s="8" t="s">
-        <v>115</v>
+      <c r="AQ3" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR3" s="8"/>
       <c r="AS3" s="8" t="s">
@@ -1830,8 +1837,8 @@
       <c r="G4" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>127</v>
+      <c r="H4" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>95</v>
@@ -1921,8 +1928,8 @@
       <c r="AP4" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="AQ4" s="8" t="s">
-        <v>127</v>
+      <c r="AQ4" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR4" s="8"/>
       <c r="AS4" s="8" t="s">
@@ -2074,8 +2081,8 @@
       <c r="G5" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>135</v>
+      <c r="H5" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>95</v>
@@ -2165,8 +2172,8 @@
       <c r="AP5" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ5" s="8" t="s">
-        <v>135</v>
+      <c r="AQ5" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR5" s="8"/>
       <c r="AS5" s="8" t="s">
@@ -2318,8 +2325,8 @@
       <c r="G6" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>144</v>
+      <c r="H6" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>95</v>
@@ -2407,8 +2414,8 @@
       <c r="AP6" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ6" s="8" t="s">
-        <v>144</v>
+      <c r="AQ6" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR6" s="8"/>
       <c r="AS6" s="8" t="s">
@@ -2556,8 +2563,8 @@
       <c r="G7" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>155</v>
+      <c r="H7" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>95</v>
@@ -2645,8 +2652,8 @@
       <c r="AP7" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ7" s="8" t="s">
-        <v>155</v>
+      <c r="AQ7" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR7" s="8"/>
       <c r="AS7" s="8" t="s">
@@ -2796,8 +2803,8 @@
       <c r="G8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>163</v>
+      <c r="H8" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>95</v>
@@ -2885,8 +2892,8 @@
       <c r="AP8" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="AQ8" s="8" t="s">
-        <v>163</v>
+      <c r="AQ8" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR8" s="8"/>
       <c r="AS8" s="8" t="s">
@@ -3036,8 +3043,8 @@
       <c r="G9" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>170</v>
+      <c r="H9" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>95</v>
@@ -3125,8 +3132,8 @@
       <c r="AP9" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="AQ9" s="8" t="s">
-        <v>170</v>
+      <c r="AQ9" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR9" s="8"/>
       <c r="AS9" s="8" t="s">
@@ -3276,8 +3283,8 @@
       <c r="G10" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>176</v>
+      <c r="H10" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>95</v>
@@ -3363,8 +3370,8 @@
       <c r="AP10" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="AQ10" s="8" t="s">
-        <v>176</v>
+      <c r="AQ10" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="AR10" s="8"/>
       <c r="AS10" s="8" t="s">
@@ -3492,8 +3499,24 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="mailto:phil@totaltmj.co.uk" xr:uid="{86F73E21-A748-4D5C-9204-BFFDAF26CE31}"/>
-    <hyperlink ref="H3" r:id="rId2" display="mailto:freddiemihranian21@gmail.com" xr:uid="{4023CBDE-4A64-4A4C-AB7A-232C95B5C818}"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{86F73E21-A748-4D5C-9204-BFFDAF26CE31}"/>
+    <hyperlink ref="H3" r:id="rId2" xr:uid="{62161F8F-4354-4DAE-AE6D-C2F17016FD76}"/>
+    <hyperlink ref="H4" r:id="rId3" xr:uid="{6C36389A-5CA5-4BF4-9B0C-830E0B9426E9}"/>
+    <hyperlink ref="H5" r:id="rId4" xr:uid="{7D68AD66-E14F-409B-82E9-E837610C84D4}"/>
+    <hyperlink ref="H6" r:id="rId5" xr:uid="{E15C7960-0F09-4EE5-8DAA-BB42EFC10168}"/>
+    <hyperlink ref="H7" r:id="rId6" xr:uid="{E68F7669-1609-42CE-85FD-F1022D62F71B}"/>
+    <hyperlink ref="H8" r:id="rId7" xr:uid="{5D481B19-73FD-4CEA-A453-421E7DAB807C}"/>
+    <hyperlink ref="H9" r:id="rId8" xr:uid="{04D8F575-9D34-4A05-AEA2-C47B78AA45A5}"/>
+    <hyperlink ref="H10" r:id="rId9" xr:uid="{08CEF6CA-B7EF-471E-B57F-ABF5E5DB9402}"/>
+    <hyperlink ref="AQ2" r:id="rId10" xr:uid="{9DBB8470-C14B-4ECD-803E-4D749BC82FF5}"/>
+    <hyperlink ref="AQ3" r:id="rId11" xr:uid="{A8426841-5CCC-48C7-8F67-CB7DD4CAC19D}"/>
+    <hyperlink ref="AQ4" r:id="rId12" xr:uid="{94E1704D-7E62-4DC7-B627-9529ECDBB7CA}"/>
+    <hyperlink ref="AQ5" r:id="rId13" xr:uid="{C87C634F-8A4C-4554-914C-5A3CDBBBB9EC}"/>
+    <hyperlink ref="AQ6" r:id="rId14" xr:uid="{BE893A78-72F9-4F35-8347-5BD977072B14}"/>
+    <hyperlink ref="AQ7" r:id="rId15" xr:uid="{F2EE8C7E-6A65-44B8-B4D7-BDF4FDA80D7B}"/>
+    <hyperlink ref="AQ8" r:id="rId16" xr:uid="{472E99FD-C4CA-4F71-91B2-5760C49DE1F6}"/>
+    <hyperlink ref="AQ9" r:id="rId17" xr:uid="{B6A26499-C444-4167-9365-00486E176E92}"/>
+    <hyperlink ref="AQ10" r:id="rId18" xr:uid="{687310CF-D28C-454F-BDDB-6A539DF8E11B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ImportSmallBatchForTest.xlsx
+++ b/ImportSmallBatchForTest.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ewer\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\currencies-co-uk\FiscalM_AImport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35AD7AE-0AA8-4EAF-ACF6-99E1C43252C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F361C3-BF1E-4B0B-9A9C-1948C952E248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="218" xr2:uid="{543EC62A-26F7-482D-96ED-BF73340C8FC4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="190">
   <si>
     <t>Lead.City</t>
   </si>
@@ -585,6 +585,30 @@
   </si>
   <si>
     <t>ewerton.mattos@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos1@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos2@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos3@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos4@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos5@lumonpay.com</t>
+  </si>
+  <si>
+    <t>ewerton.mattos6@lumonpay.com</t>
+  </si>
+  <si>
+    <t>patrick.darling@lumonpay.com</t>
+  </si>
+  <si>
+    <t>Mario.AlexandreCosta@lumonpay.com</t>
   </si>
 </sst>
 </file>
@@ -1063,8 +1087,8 @@
   <dimension ref="A1:CL10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="25.42578125" customWidth="1"/>
+    <col min="8" max="8" width="35.85546875" customWidth="1"/>
+    <col min="43" max="43" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:90" x14ac:dyDescent="0.25">
@@ -1598,7 +1622,7 @@
         <v>93</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>95</v>
@@ -1687,7 +1711,7 @@
         <v>92</v>
       </c>
       <c r="AQ3" s="10" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AR3" s="8"/>
       <c r="AS3" s="8" t="s">
@@ -1838,7 +1862,7 @@
         <v>93</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>95</v>
@@ -1929,7 +1953,7 @@
         <v>126</v>
       </c>
       <c r="AQ4" s="10" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AR4" s="8"/>
       <c r="AS4" s="8" t="s">
@@ -2082,7 +2106,7 @@
         <v>93</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>95</v>
@@ -2173,7 +2197,7 @@
         <v>92</v>
       </c>
       <c r="AQ5" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AR5" s="8"/>
       <c r="AS5" s="8" t="s">
@@ -2326,7 +2350,7 @@
         <v>93</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>95</v>
@@ -2415,7 +2439,7 @@
         <v>92</v>
       </c>
       <c r="AQ6" s="10" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AR6" s="8"/>
       <c r="AS6" s="8" t="s">
@@ -2564,7 +2588,7 @@
         <v>93</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>95</v>
@@ -2653,7 +2677,7 @@
         <v>92</v>
       </c>
       <c r="AQ7" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AR7" s="8"/>
       <c r="AS7" s="8" t="s">
@@ -2804,7 +2828,7 @@
         <v>93</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>95</v>
@@ -2893,7 +2917,7 @@
         <v>126</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AR8" s="8"/>
       <c r="AS8" s="8" t="s">
@@ -3044,7 +3068,7 @@
         <v>93</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>95</v>
@@ -3133,7 +3157,7 @@
         <v>126</v>
       </c>
       <c r="AQ9" s="10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AR9" s="8"/>
       <c r="AS9" s="8" t="s">
@@ -3284,7 +3308,7 @@
         <v>93</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>95</v>
@@ -3371,7 +3395,7 @@
         <v>92</v>
       </c>
       <c r="AQ10" s="10" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="AR10" s="8"/>
       <c r="AS10" s="8" t="s">
@@ -3500,23 +3524,19 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{86F73E21-A748-4D5C-9204-BFFDAF26CE31}"/>
-    <hyperlink ref="H3" r:id="rId2" xr:uid="{62161F8F-4354-4DAE-AE6D-C2F17016FD76}"/>
-    <hyperlink ref="H4" r:id="rId3" xr:uid="{6C36389A-5CA5-4BF4-9B0C-830E0B9426E9}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{7D68AD66-E14F-409B-82E9-E837610C84D4}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{E15C7960-0F09-4EE5-8DAA-BB42EFC10168}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{E68F7669-1609-42CE-85FD-F1022D62F71B}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{5D481B19-73FD-4CEA-A453-421E7DAB807C}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{04D8F575-9D34-4A05-AEA2-C47B78AA45A5}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{08CEF6CA-B7EF-471E-B57F-ABF5E5DB9402}"/>
-    <hyperlink ref="AQ2" r:id="rId10" xr:uid="{9DBB8470-C14B-4ECD-803E-4D749BC82FF5}"/>
-    <hyperlink ref="AQ3" r:id="rId11" xr:uid="{A8426841-5CCC-48C7-8F67-CB7DD4CAC19D}"/>
-    <hyperlink ref="AQ4" r:id="rId12" xr:uid="{94E1704D-7E62-4DC7-B627-9529ECDBB7CA}"/>
-    <hyperlink ref="AQ5" r:id="rId13" xr:uid="{C87C634F-8A4C-4554-914C-5A3CDBBBB9EC}"/>
-    <hyperlink ref="AQ6" r:id="rId14" xr:uid="{BE893A78-72F9-4F35-8347-5BD977072B14}"/>
-    <hyperlink ref="AQ7" r:id="rId15" xr:uid="{F2EE8C7E-6A65-44B8-B4D7-BDF4FDA80D7B}"/>
-    <hyperlink ref="AQ8" r:id="rId16" xr:uid="{472E99FD-C4CA-4F71-91B2-5760C49DE1F6}"/>
-    <hyperlink ref="AQ9" r:id="rId17" xr:uid="{B6A26499-C444-4167-9365-00486E176E92}"/>
-    <hyperlink ref="AQ10" r:id="rId18" xr:uid="{687310CF-D28C-454F-BDDB-6A539DF8E11B}"/>
+    <hyperlink ref="H5" r:id="rId2" xr:uid="{7D68AD66-E14F-409B-82E9-E837610C84D4}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{E15C7960-0F09-4EE5-8DAA-BB42EFC10168}"/>
+    <hyperlink ref="H7" r:id="rId4" xr:uid="{E68F7669-1609-42CE-85FD-F1022D62F71B}"/>
+    <hyperlink ref="H8" r:id="rId5" xr:uid="{5D481B19-73FD-4CEA-A453-421E7DAB807C}"/>
+    <hyperlink ref="H9" r:id="rId6" xr:uid="{04D8F575-9D34-4A05-AEA2-C47B78AA45A5}"/>
+    <hyperlink ref="H10" r:id="rId7" xr:uid="{08CEF6CA-B7EF-471E-B57F-ABF5E5DB9402}"/>
+    <hyperlink ref="AQ2" r:id="rId8" xr:uid="{B4CE8F2D-D18B-4EB7-897A-4740F8DC616D}"/>
+    <hyperlink ref="AQ5" r:id="rId9" xr:uid="{80CC2C5C-BC92-4022-AB8F-922EF76E3DDE}"/>
+    <hyperlink ref="AQ6" r:id="rId10" xr:uid="{16E0480F-0BF9-4D2D-B574-8B247542FF87}"/>
+    <hyperlink ref="AQ7" r:id="rId11" xr:uid="{165845D5-009D-4CA7-95D8-9FA663E9EFCC}"/>
+    <hyperlink ref="AQ8" r:id="rId12" xr:uid="{5CD62BCD-ABC0-4405-88F2-0D54EFDFCA30}"/>
+    <hyperlink ref="AQ9" r:id="rId13" xr:uid="{D01BAED2-63ED-41E1-96F8-AC8DC0210CA6}"/>
+    <hyperlink ref="AQ10" r:id="rId14" xr:uid="{90EB5984-F7BA-4DD6-83B0-A0B3C702A663}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ImportSmallBatchForTest.xlsx
+++ b/ImportSmallBatchForTest.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mario\source\repos\FiscalM_AImport1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA622A1-9269-466A-951C-9AEE10A95918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5337B7-53AF-42B2-A2CC-FC38E6706408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="218" xr2:uid="{543EC62A-26F7-482D-96ED-BF73340C8FC4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="218" xr2:uid="{543EC62A-26F7-482D-96ED-BF73340C8FC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="314">
   <si>
     <t>Lead.CountryMobile</t>
   </si>
@@ -732,36 +732,21 @@
     <t>account.chl_usclient</t>
   </si>
   <si>
-    <t>UATTEST-22</t>
-  </si>
-  <si>
     <t>40735402-8ed1-ef11-a72f-0022481b0c50</t>
   </si>
   <si>
     <t>0bb067b8-b240-f111-bec6-002248c899f8</t>
   </si>
   <si>
-    <t>UATTEST-81</t>
-  </si>
-  <si>
     <t>23/5/1974</t>
   </si>
   <si>
-    <t>UATTEST-82</t>
-  </si>
-  <si>
     <t>27/8/1992</t>
   </si>
   <si>
-    <t>UATTEST-83</t>
-  </si>
-  <si>
     <t>17/4/1987</t>
   </si>
   <si>
-    <t>UATTEST-84</t>
-  </si>
-  <si>
     <t>lead.chl_division</t>
   </si>
   <si>
@@ -840,9 +825,6 @@
     <t>Diana</t>
   </si>
   <si>
-    <t>UATTEST-85</t>
-  </si>
-  <si>
     <t>Raynor</t>
   </si>
   <si>
@@ -864,9 +846,6 @@
     <t>Shaheen</t>
   </si>
   <si>
-    <t>UATTEST-86</t>
-  </si>
-  <si>
     <t>Shaik</t>
   </si>
   <si>
@@ -888,9 +867,6 @@
     <t>Chikodili</t>
   </si>
   <si>
-    <t>UATTEST-87</t>
-  </si>
-  <si>
     <t>Umeaka</t>
   </si>
   <si>
@@ -906,9 +882,6 @@
     <t>Michael</t>
   </si>
   <si>
-    <t>UATTEST-88</t>
-  </si>
-  <si>
     <t>kfoury</t>
   </si>
   <si>
@@ -930,9 +903,6 @@
     <t>Shady</t>
   </si>
   <si>
-    <t>UATTEST-90</t>
-  </si>
-  <si>
     <t>Wahbi</t>
   </si>
   <si>
@@ -984,31 +954,34 @@
     <t>yes</t>
   </si>
   <si>
-    <t>Leicester</t>
-  </si>
-  <si>
-    <t>20/8/1969</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>UATTEST-101</t>
-  </si>
-  <si>
-    <t>Russell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Guinevere Way  </t>
-  </si>
-  <si>
-    <t>LE3 3RN</t>
-  </si>
-  <si>
-    <t>James Russell</t>
-  </si>
-  <si>
-    <t>test11@test45617.co.uk</t>
+    <t>P70000022</t>
+  </si>
+  <si>
+    <t>P70000081</t>
+  </si>
+  <si>
+    <t>P70000082</t>
+  </si>
+  <si>
+    <t>P70000083</t>
+  </si>
+  <si>
+    <t>P70000084</t>
+  </si>
+  <si>
+    <t>P70000085</t>
+  </si>
+  <si>
+    <t>P70000086</t>
+  </si>
+  <si>
+    <t>P70000087</t>
+  </si>
+  <si>
+    <t>P70000088</t>
+  </si>
+  <si>
+    <t>P70000090</t>
   </si>
 </sst>
 </file>
@@ -1718,16 +1691,16 @@
         <v>131</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AP1" s="2" t="s">
         <v>132</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AR1" s="2" t="s">
         <v>22</v>
@@ -1745,16 +1718,16 @@
         <v>24</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="AY1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="BA1" s="1" t="s">
         <v>26</v>
@@ -1866,7 +1839,7 @@
         <v>49</v>
       </c>
       <c r="CL1" s="4" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="CM1" s="4" t="s">
         <v>50</v>
@@ -1934,7 +1907,7 @@
         <v>61</v>
       </c>
       <c r="DJ1" s="5" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="DK1" s="5" t="s">
         <v>62</v>
@@ -1991,7 +1964,7 @@
         <v>69</v>
       </c>
       <c r="EC1" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="ED1" s="8"/>
     </row>
@@ -2019,11 +1992,11 @@
       </c>
       <c r="J2" s="22"/>
       <c r="K2" s="22" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="22" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="N2" s="22" t="s">
         <v>164</v>
@@ -2039,7 +2012,7 @@
         <v>167</v>
       </c>
       <c r="S2" s="22" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="T2" s="22" t="s">
         <v>168</v>
@@ -2086,7 +2059,7 @@
       </c>
       <c r="AM2" s="23"/>
       <c r="AN2" s="23" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AO2" s="24"/>
       <c r="AP2" s="23" t="s">
@@ -2264,7 +2237,7 @@
       </c>
       <c r="DS2" s="23"/>
       <c r="DT2" s="23" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="DU2" s="23"/>
       <c r="DV2" s="23" t="s">
@@ -2320,8 +2293,8 @@
       <c r="L3" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>243</v>
+      <c r="M3" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="N3" s="8">
         <v>0</v>
@@ -2334,17 +2307,17 @@
         <v>75000</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="S3" s="8">
         <v>22</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="U3" s="8"/>
       <c r="V3" s="7" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="W3" s="7">
         <v>126670008</v>
@@ -2365,8 +2338,8 @@
         <v>7468413877</v>
       </c>
       <c r="AE3" s="8"/>
-      <c r="AF3" s="8" t="s">
-        <v>231</v>
+      <c r="AF3" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG3" s="8" t="s">
         <v>77</v>
@@ -2383,8 +2356,8 @@
       <c r="AK3" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL3" s="8" t="s">
-        <v>231</v>
+      <c r="AL3" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM3" s="8" t="s">
         <v>77</v>
@@ -2404,8 +2377,8 @@
       <c r="AR3" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="AS3" s="8" t="s">
-        <v>232</v>
+      <c r="AS3" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT3" s="7" t="s">
         <v>81</v>
@@ -2414,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW3" s="7" t="s">
         <v>83</v>
@@ -2461,7 +2434,7 @@
         <v>72</v>
       </c>
       <c r="BM3" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="BN3" s="8"/>
       <c r="BO3" s="8" t="s">
@@ -2475,10 +2448,10 @@
         <v>75000</v>
       </c>
       <c r="BS3" s="14" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BT3" s="8" t="s">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="BU3" s="8"/>
       <c r="BV3" s="8">
@@ -2488,7 +2461,7 @@
         <v>85</v>
       </c>
       <c r="BX3" s="14" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="BY3" s="8">
         <v>126670037</v>
@@ -2504,8 +2477,8 @@
       <c r="CD3" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="CE3" s="8" t="s">
-        <v>231</v>
+      <c r="CE3" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF3" s="18" t="s">
         <v>77</v>
@@ -2539,7 +2512,7 @@
         <v>80</v>
       </c>
       <c r="CQ3" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR3" s="16" t="s">
         <v>81</v>
@@ -2599,13 +2572,13 @@
         <v>74</v>
       </c>
       <c r="DK3" s="8" t="s">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="DL3" s="8">
         <v>7468413877</v>
       </c>
       <c r="DM3" s="8" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="DN3" s="8">
         <v>126670037</v>
@@ -2629,16 +2602,16 @@
         <v>1</v>
       </c>
       <c r="DU3" s="8" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="DV3" s="8">
         <v>126670021</v>
       </c>
       <c r="DW3" s="8" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="DX3" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY3" s="8" t="s">
         <v>81</v>
@@ -2694,8 +2667,8 @@
       <c r="L4" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="M4" s="8" t="s">
-        <v>244</v>
+      <c r="M4" s="10" t="s">
+        <v>239</v>
       </c>
       <c r="N4" s="8">
         <v>0</v>
@@ -2708,17 +2681,17 @@
         <v>75000</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="S4" s="8">
         <v>81</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>233</v>
+        <v>305</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="W4" s="8">
         <v>126670008</v>
@@ -2739,8 +2712,8 @@
         <v>7403369396</v>
       </c>
       <c r="AE4" s="8"/>
-      <c r="AF4" s="8" t="s">
-        <v>231</v>
+      <c r="AF4" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG4" s="8" t="s">
         <v>77</v>
@@ -2757,8 +2730,8 @@
       <c r="AK4" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="AL4" s="8" t="s">
-        <v>231</v>
+      <c r="AL4" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM4" s="8" t="s">
         <v>77</v>
@@ -2778,8 +2751,8 @@
       <c r="AR4" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="AS4" s="8" t="s">
-        <v>232</v>
+      <c r="AS4" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT4" s="8" t="s">
         <v>81</v>
@@ -2788,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="AV4" s="8" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW4" s="8" t="s">
         <v>83</v>
@@ -2837,7 +2810,7 @@
         <v>72</v>
       </c>
       <c r="BM4" s="8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="BN4" s="8"/>
       <c r="BO4" s="8" t="s">
@@ -2851,10 +2824,10 @@
         <v>75000</v>
       </c>
       <c r="BS4" s="8" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="BT4" s="8" t="s">
-        <v>233</v>
+        <v>305</v>
       </c>
       <c r="BU4" s="8"/>
       <c r="BV4" s="8">
@@ -2864,7 +2837,7 @@
         <v>95</v>
       </c>
       <c r="BX4" s="8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="BY4" s="8">
         <v>126670037</v>
@@ -2880,8 +2853,8 @@
       <c r="CD4" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="CE4" s="8" t="s">
-        <v>231</v>
+      <c r="CE4" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF4" s="18" t="s">
         <v>77</v>
@@ -2915,7 +2888,7 @@
         <v>93</v>
       </c>
       <c r="CQ4" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR4" s="16" t="s">
         <v>81</v>
@@ -2975,13 +2948,13 @@
         <v>74</v>
       </c>
       <c r="DK4" s="8" t="s">
-        <v>233</v>
+        <v>305</v>
       </c>
       <c r="DL4" s="8">
         <v>7403369396</v>
       </c>
       <c r="DM4" s="8" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="DN4" s="8">
         <v>126670037</v>
@@ -3014,7 +2987,7 @@
         <v>97</v>
       </c>
       <c r="DX4" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY4" s="8" t="s">
         <v>81</v>
@@ -3056,7 +3029,7 @@
         <v>44</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I5" s="8">
         <v>126670185</v>
@@ -3071,7 +3044,7 @@
         <v>73</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N5" s="8">
         <v>0</v>
@@ -3084,17 +3057,17 @@
         <v>75000</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="S5" s="8">
         <v>82</v>
       </c>
       <c r="T5" s="8" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="W5" s="8">
         <v>126670008</v>
@@ -3117,8 +3090,8 @@
       <c r="AE5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="AF5" s="8" t="s">
-        <v>231</v>
+      <c r="AF5" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG5" s="8" t="s">
         <v>101</v>
@@ -3135,8 +3108,8 @@
       <c r="AK5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL5" s="8" t="s">
-        <v>231</v>
+      <c r="AL5" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM5" s="8" t="s">
         <v>101</v>
@@ -3156,8 +3129,8 @@
       <c r="AR5" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="AS5" s="8" t="s">
-        <v>232</v>
+      <c r="AS5" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT5" s="7" t="s">
         <v>81</v>
@@ -3166,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="AV5" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW5" s="8" t="s">
         <v>83</v>
@@ -3206,7 +3179,7 @@
         <v>44</v>
       </c>
       <c r="BJ5" s="8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="BK5" s="8">
         <v>126670185</v>
@@ -3215,7 +3188,7 @@
         <v>99</v>
       </c>
       <c r="BM5" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="BN5" s="8"/>
       <c r="BO5" s="8" t="s">
@@ -3229,10 +3202,10 @@
         <v>75000</v>
       </c>
       <c r="BS5" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="BT5" s="8" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="BU5" s="8"/>
       <c r="BV5" s="8">
@@ -3242,7 +3215,7 @@
         <v>95</v>
       </c>
       <c r="BX5" s="8" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="BY5" s="8">
         <v>126670037</v>
@@ -3260,8 +3233,8 @@
       <c r="CD5" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="CE5" s="8" t="s">
-        <v>231</v>
+      <c r="CE5" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF5" s="18" t="s">
         <v>101</v>
@@ -3295,7 +3268,7 @@
         <v>102</v>
       </c>
       <c r="CQ5" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR5" s="16" t="s">
         <v>81</v>
@@ -3355,13 +3328,13 @@
         <v>74</v>
       </c>
       <c r="DK5" s="8" t="s">
-        <v>235</v>
+        <v>306</v>
       </c>
       <c r="DL5" s="8">
         <v>7710355595</v>
       </c>
       <c r="DM5" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="DN5" s="8">
         <v>126670037</v>
@@ -3394,7 +3367,7 @@
         <v>97</v>
       </c>
       <c r="DX5" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY5" s="8" t="s">
         <v>81</v>
@@ -3436,7 +3409,7 @@
         <v>44</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I6" s="8">
         <v>126670000</v>
@@ -3451,7 +3424,7 @@
         <v>73</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="N6" s="8">
         <v>0</v>
@@ -3464,17 +3437,17 @@
         <v>75000</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="S6" s="8">
         <v>83</v>
       </c>
       <c r="T6" s="8" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="W6" s="8">
         <v>126670008</v>
@@ -3497,8 +3470,8 @@
         <v>7770075075</v>
       </c>
       <c r="AE6" s="8"/>
-      <c r="AF6" s="8" t="s">
-        <v>231</v>
+      <c r="AF6" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>77</v>
@@ -3515,8 +3488,8 @@
       <c r="AK6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL6" s="8" t="s">
-        <v>231</v>
+      <c r="AL6" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>77</v>
@@ -3536,8 +3509,8 @@
       <c r="AR6" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="AS6" s="8" t="s">
-        <v>232</v>
+      <c r="AS6" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT6" s="7" t="s">
         <v>81</v>
@@ -3546,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="AV6" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW6" s="8" t="s">
         <v>83</v>
@@ -3586,7 +3559,7 @@
         <v>44</v>
       </c>
       <c r="BJ6" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="BK6" s="8">
         <v>126670000</v>
@@ -3595,7 +3568,7 @@
         <v>72</v>
       </c>
       <c r="BM6" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="BN6" s="8"/>
       <c r="BO6" s="8" t="s">
@@ -3609,10 +3582,10 @@
         <v>75000</v>
       </c>
       <c r="BS6" s="8" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="BT6" s="8" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="BU6" s="8"/>
       <c r="BV6" s="8">
@@ -3622,7 +3595,7 @@
         <v>95</v>
       </c>
       <c r="BX6" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="BY6" s="8">
         <v>126670037</v>
@@ -3640,8 +3613,8 @@
       <c r="CD6" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="CE6" s="8" t="s">
-        <v>231</v>
+      <c r="CE6" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF6" s="18" t="s">
         <v>77</v>
@@ -3675,7 +3648,7 @@
         <v>106</v>
       </c>
       <c r="CQ6" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR6" s="16" t="s">
         <v>81</v>
@@ -3702,7 +3675,7 @@
         <v>107</v>
       </c>
       <c r="CZ6" s="8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="DA6" s="8">
         <v>126670001</v>
@@ -3735,13 +3708,13 @@
         <v>74</v>
       </c>
       <c r="DK6" s="8" t="s">
-        <v>237</v>
+        <v>307</v>
       </c>
       <c r="DL6" s="8">
         <v>7770075075</v>
       </c>
       <c r="DM6" s="8" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="DN6" s="8">
         <v>126670037</v>
@@ -3774,7 +3747,7 @@
         <v>97</v>
       </c>
       <c r="DX6" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY6" s="8" t="s">
         <v>81</v>
@@ -3816,7 +3789,7 @@
         <v>971</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I7" s="8">
         <v>126670000</v>
@@ -3831,7 +3804,7 @@
         <v>73</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="N7" s="8">
         <v>0</v>
@@ -3844,17 +3817,17 @@
         <v>75000</v>
       </c>
       <c r="R7" s="8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="S7" s="8">
         <v>84</v>
       </c>
       <c r="T7" s="8" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="U7" s="8"/>
       <c r="V7" s="8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="W7" s="8">
         <v>126670008</v>
@@ -3877,8 +3850,8 @@
       <c r="AE7" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="AF7" s="8" t="s">
-        <v>231</v>
+      <c r="AF7" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG7" s="7" t="s">
         <v>77</v>
@@ -3895,8 +3868,8 @@
       <c r="AK7" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL7" s="8" t="s">
-        <v>231</v>
+      <c r="AL7" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM7" s="7" t="s">
         <v>77</v>
@@ -3916,8 +3889,8 @@
       <c r="AR7" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="AS7" s="8" t="s">
-        <v>232</v>
+      <c r="AS7" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT7" s="7" t="s">
         <v>81</v>
@@ -3926,7 +3899,7 @@
         <v>1</v>
       </c>
       <c r="AV7" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW7" s="8" t="s">
         <v>113</v>
@@ -3964,7 +3937,7 @@
         <v>971</v>
       </c>
       <c r="BJ7" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="BK7" s="8">
         <v>126670000</v>
@@ -3973,7 +3946,7 @@
         <v>72</v>
       </c>
       <c r="BM7" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="BN7" s="8"/>
       <c r="BO7" s="8" t="s">
@@ -3987,16 +3960,16 @@
         <v>75000</v>
       </c>
       <c r="BS7" s="8" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="BT7" s="8" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="BU7" s="8"/>
       <c r="BV7" s="8"/>
       <c r="BW7" s="21"/>
       <c r="BX7" s="8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="BY7" s="8">
         <v>126670037</v>
@@ -4014,8 +3987,8 @@
       <c r="CD7" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="CE7" s="8" t="s">
-        <v>231</v>
+      <c r="CE7" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF7" s="18" t="s">
         <v>77</v>
@@ -4049,7 +4022,7 @@
         <v>112</v>
       </c>
       <c r="CQ7" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR7" s="16" t="s">
         <v>81</v>
@@ -4107,13 +4080,13 @@
         <v>74</v>
       </c>
       <c r="DK7" s="8" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
       <c r="DL7" s="8">
         <v>570000000</v>
       </c>
       <c r="DM7" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="DN7" s="8">
         <v>126670037</v>
@@ -4146,7 +4119,7 @@
         <v>116</v>
       </c>
       <c r="DX7" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY7" s="8" t="s">
         <v>81</v>
@@ -4167,7 +4140,7 @@
     </row>
     <row r="8" spans="1:134" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B8" s="8">
         <v>126670001</v>
@@ -4203,7 +4176,7 @@
         <v>73</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="N8" s="8">
         <v>0</v>
@@ -4216,17 +4189,17 @@
         <v>75000</v>
       </c>
       <c r="R8" s="8" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="S8" s="8">
         <v>85</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="U8" s="8"/>
       <c r="V8" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="W8" s="8">
         <v>126670008</v>
@@ -4247,8 +4220,8 @@
         <v>7484717532</v>
       </c>
       <c r="AE8" s="8"/>
-      <c r="AF8" s="8" t="s">
-        <v>231</v>
+      <c r="AF8" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG8" s="8" t="s">
         <v>101</v>
@@ -4265,8 +4238,8 @@
       <c r="AK8" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL8" s="8" t="s">
-        <v>231</v>
+      <c r="AL8" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM8" s="8" t="s">
         <v>101</v>
@@ -4284,10 +4257,10 @@
         <v>92</v>
       </c>
       <c r="AR8" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="AS8" s="8" t="s">
-        <v>232</v>
+        <v>262</v>
+      </c>
+      <c r="AS8" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT8" s="7" t="s">
         <v>81</v>
@@ -4296,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="AV8" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW8" s="8" t="s">
         <v>113</v>
@@ -4311,10 +4284,10 @@
         <v>74</v>
       </c>
       <c r="BA8" s="12" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="BB8" s="8" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="BC8" s="8">
         <v>126670001</v>
@@ -4345,7 +4318,7 @@
         <v>72</v>
       </c>
       <c r="BM8" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="BN8" s="8"/>
       <c r="BO8" s="8" t="s">
@@ -4359,10 +4332,10 @@
         <v>75000</v>
       </c>
       <c r="BS8" s="8" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="BT8" s="8" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="BU8" s="8"/>
       <c r="BV8" s="8">
@@ -4372,7 +4345,7 @@
         <v>95</v>
       </c>
       <c r="BX8" s="8" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="BY8" s="8">
         <v>126670037</v>
@@ -4386,16 +4359,16 @@
       </c>
       <c r="CC8" s="8"/>
       <c r="CD8" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="CE8" s="8" t="s">
-        <v>231</v>
+        <v>264</v>
+      </c>
+      <c r="CE8" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF8" s="18" t="s">
         <v>101</v>
       </c>
       <c r="CG8" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="CH8" s="8"/>
       <c r="CI8" s="8">
@@ -4420,10 +4393,10 @@
         <v>97</v>
       </c>
       <c r="CP8" s="8" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="CQ8" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR8" s="16" t="s">
         <v>81</v>
@@ -4447,10 +4420,10 @@
         <v>74</v>
       </c>
       <c r="CY8" s="8" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="CZ8" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="DA8" s="8">
         <v>126670001</v>
@@ -4483,13 +4456,13 @@
         <v>74</v>
       </c>
       <c r="DK8" s="8" t="s">
-        <v>266</v>
+        <v>309</v>
       </c>
       <c r="DL8" s="8">
         <v>7484717532</v>
       </c>
       <c r="DM8" s="8" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="DN8" s="8">
         <v>126670037</v>
@@ -4498,10 +4471,10 @@
         <v>76</v>
       </c>
       <c r="DP8" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="DQ8" s="8" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="DR8" s="8">
         <v>126670011</v>
@@ -4522,7 +4495,7 @@
         <v>97</v>
       </c>
       <c r="DX8" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY8" s="8" t="s">
         <v>81</v>
@@ -4543,7 +4516,7 @@
     </row>
     <row r="9" spans="1:134" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B9" s="8">
         <v>126670001</v>
@@ -4555,7 +4528,7 @@
         <v>126670224</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F9" s="8">
         <v>126670232</v>
@@ -4579,7 +4552,7 @@
         <v>73</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="N9" s="8">
         <v>0</v>
@@ -4592,17 +4565,17 @@
         <v>75000</v>
       </c>
       <c r="R9" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="S9" s="8">
         <v>86</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="U9" s="8"/>
       <c r="V9" s="8" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="W9" s="8">
         <v>126670008</v>
@@ -4623,8 +4596,8 @@
         <v>7624241996</v>
       </c>
       <c r="AE9" s="8"/>
-      <c r="AF9" s="8" t="s">
-        <v>231</v>
+      <c r="AF9" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG9" s="7" t="s">
         <v>77</v>
@@ -4633,7 +4606,7 @@
         <v>126670026</v>
       </c>
       <c r="AI9" s="8" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="AJ9" s="7">
         <v>0</v>
@@ -4641,8 +4614,8 @@
       <c r="AK9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL9" s="8" t="s">
-        <v>231</v>
+      <c r="AL9" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM9" s="7" t="s">
         <v>77</v>
@@ -4660,10 +4633,10 @@
         <v>92</v>
       </c>
       <c r="AR9" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="AS9" s="8" t="s">
-        <v>232</v>
+        <v>270</v>
+      </c>
+      <c r="AS9" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT9" s="7" t="s">
         <v>81</v>
@@ -4672,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="AV9" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW9" s="8" t="s">
         <v>83</v>
@@ -4687,10 +4660,10 @@
         <v>74</v>
       </c>
       <c r="BA9" s="12" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="BB9" s="8" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="BC9" s="8">
         <v>126670001</v>
@@ -4703,7 +4676,7 @@
         <v>126670224</v>
       </c>
       <c r="BG9" s="8" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="BH9" s="8">
         <v>126670232</v>
@@ -4721,7 +4694,7 @@
         <v>99</v>
       </c>
       <c r="BM9" s="8" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="BN9" s="8"/>
       <c r="BO9" s="8" t="s">
@@ -4735,10 +4708,10 @@
         <v>75000</v>
       </c>
       <c r="BS9" s="8" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="BT9" s="8" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="BU9" s="8"/>
       <c r="BV9" s="8">
@@ -4748,7 +4721,7 @@
         <v>95</v>
       </c>
       <c r="BX9" s="8" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="BY9" s="8">
         <v>126670037</v>
@@ -4762,23 +4735,23 @@
       </c>
       <c r="CC9" s="8"/>
       <c r="CD9" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="CE9" s="8" t="s">
-        <v>231</v>
+        <v>272</v>
+      </c>
+      <c r="CE9" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF9" s="18" t="s">
         <v>77</v>
       </c>
       <c r="CG9" s="8" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="CH9" s="8"/>
       <c r="CI9" s="8">
         <v>126670026</v>
       </c>
       <c r="CJ9" s="8" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="CK9" s="8">
         <v>0</v>
@@ -4796,10 +4769,10 @@
         <v>97</v>
       </c>
       <c r="CP9" s="8" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="CQ9" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR9" s="16" t="s">
         <v>81</v>
@@ -4823,10 +4796,10 @@
         <v>74</v>
       </c>
       <c r="CY9" s="8" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="CZ9" s="8" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="DA9" s="8">
         <v>126670001</v>
@@ -4859,13 +4832,13 @@
         <v>74</v>
       </c>
       <c r="DK9" s="8" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="DL9" s="8">
         <v>7624241996</v>
       </c>
       <c r="DM9" s="8" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="DN9" s="8">
         <v>126670037</v>
@@ -4874,16 +4847,16 @@
         <v>76</v>
       </c>
       <c r="DP9" s="8" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="DQ9" s="8" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="DR9" s="8">
         <v>126670026</v>
       </c>
       <c r="DS9" s="8" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="DT9" s="8">
         <v>0</v>
@@ -4898,7 +4871,7 @@
         <v>97</v>
       </c>
       <c r="DX9" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY9" s="8" t="s">
         <v>81</v>
@@ -4940,7 +4913,7 @@
         <v>44</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="I10" s="8">
         <v>126670185</v>
@@ -4955,7 +4928,7 @@
         <v>73</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="N10" s="8">
         <v>0</v>
@@ -4968,17 +4941,17 @@
         <v>75000</v>
       </c>
       <c r="R10" s="8" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="S10" s="8">
         <v>87</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="W10" s="8">
         <v>126670008</v>
@@ -4999,8 +4972,8 @@
         <v>7450201775</v>
       </c>
       <c r="AE10" s="8"/>
-      <c r="AF10" s="8" t="s">
-        <v>231</v>
+      <c r="AF10" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG10" s="7" t="s">
         <v>77</v>
@@ -5017,8 +4990,8 @@
       <c r="AK10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL10" s="8" t="s">
-        <v>231</v>
+      <c r="AL10" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM10" s="7" t="s">
         <v>77</v>
@@ -5036,10 +5009,10 @@
         <v>92</v>
       </c>
       <c r="AR10" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="AS10" s="8" t="s">
-        <v>232</v>
+        <v>276</v>
+      </c>
+      <c r="AS10" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT10" s="7" t="s">
         <v>81</v>
@@ -5048,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="AV10" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW10" s="8" t="s">
         <v>83</v>
@@ -5063,7 +5036,7 @@
         <v>74</v>
       </c>
       <c r="BA10" s="12" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="BB10" s="8" t="s">
         <v>90</v>
@@ -5088,7 +5061,7 @@
         <v>44</v>
       </c>
       <c r="BJ10" s="8" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="BK10" s="8">
         <v>126670185</v>
@@ -5097,7 +5070,7 @@
         <v>99</v>
       </c>
       <c r="BM10" s="8" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="BN10" s="8"/>
       <c r="BO10" s="8" t="s">
@@ -5111,10 +5084,10 @@
         <v>75000</v>
       </c>
       <c r="BS10" s="8" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="BT10" s="8" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="BU10" s="8"/>
       <c r="BV10" s="8">
@@ -5124,7 +5097,7 @@
         <v>95</v>
       </c>
       <c r="BX10" s="8" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="BY10" s="8">
         <v>126670037</v>
@@ -5138,16 +5111,16 @@
       </c>
       <c r="CC10" s="8"/>
       <c r="CD10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="CE10" s="8" t="s">
-        <v>231</v>
+        <v>278</v>
+      </c>
+      <c r="CE10" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF10" s="18" t="s">
         <v>77</v>
       </c>
       <c r="CG10" s="8" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="CH10" s="8"/>
       <c r="CI10" s="8">
@@ -5172,10 +5145,10 @@
         <v>97</v>
       </c>
       <c r="CP10" s="8" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="CQ10" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR10" s="16" t="s">
         <v>81</v>
@@ -5199,10 +5172,10 @@
         <v>74</v>
       </c>
       <c r="CY10" s="8" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="CZ10" s="8" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="DA10" s="8">
         <v>126670001</v>
@@ -5235,13 +5208,13 @@
         <v>74</v>
       </c>
       <c r="DK10" s="8" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="DL10" s="8">
         <v>7450201775</v>
       </c>
       <c r="DM10" s="8" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="DN10" s="8">
         <v>126670037</v>
@@ -5250,10 +5223,10 @@
         <v>76</v>
       </c>
       <c r="DP10" s="8" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="DQ10" s="8" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="DR10" s="8">
         <v>126670037</v>
@@ -5274,7 +5247,7 @@
         <v>97</v>
       </c>
       <c r="DX10" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY10" s="8" t="s">
         <v>81</v>
@@ -5331,7 +5304,7 @@
         <v>73</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="N11" s="8">
         <v>0</v>
@@ -5344,17 +5317,17 @@
         <v>75000</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="S11" s="8">
         <v>88</v>
       </c>
       <c r="T11" s="8" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="W11" s="8">
         <v>126670008</v>
@@ -5375,8 +5348,8 @@
         <v>567000000</v>
       </c>
       <c r="AE11" s="8"/>
-      <c r="AF11" s="8" t="s">
-        <v>231</v>
+      <c r="AF11" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG11" s="7" t="s">
         <v>77</v>
@@ -5393,8 +5366,8 @@
       <c r="AK11" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL11" s="8" t="s">
-        <v>231</v>
+      <c r="AL11" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM11" s="7" t="s">
         <v>77</v>
@@ -5412,10 +5385,10 @@
         <v>92</v>
       </c>
       <c r="AR11" s="12" t="s">
-        <v>290</v>
-      </c>
-      <c r="AS11" s="8" t="s">
-        <v>232</v>
+        <v>281</v>
+      </c>
+      <c r="AS11" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT11" s="7" t="s">
         <v>81</v>
@@ -5424,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="AV11" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW11" s="8" t="s">
         <v>83</v>
@@ -5471,7 +5444,7 @@
         <v>72</v>
       </c>
       <c r="BM11" s="8" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="BN11" s="8"/>
       <c r="BO11" s="8" t="s">
@@ -5485,10 +5458,10 @@
         <v>75000</v>
       </c>
       <c r="BS11" s="8" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="BT11" s="8" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="BU11" s="8"/>
       <c r="BV11" s="8">
@@ -5498,7 +5471,7 @@
         <v>95</v>
       </c>
       <c r="BX11" s="8" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="BY11" s="8">
         <v>126670037</v>
@@ -5512,16 +5485,16 @@
       </c>
       <c r="CC11" s="8"/>
       <c r="CD11" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="CE11" s="8" t="s">
-        <v>231</v>
+        <v>282</v>
+      </c>
+      <c r="CE11" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF11" s="18" t="s">
         <v>77</v>
       </c>
       <c r="CG11" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="CH11" s="8"/>
       <c r="CI11" s="8">
@@ -5546,10 +5519,10 @@
         <v>97</v>
       </c>
       <c r="CP11" s="8" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="CQ11" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR11" s="16" t="s">
         <v>81</v>
@@ -5574,7 +5547,7 @@
       </c>
       <c r="CY11" s="9"/>
       <c r="CZ11" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="DA11" s="8">
         <v>126670001</v>
@@ -5607,13 +5580,13 @@
         <v>74</v>
       </c>
       <c r="DK11" s="8" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="DL11" s="8">
         <v>567000000</v>
       </c>
       <c r="DM11" s="8" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="DN11" s="8">
         <v>126670037</v>
@@ -5622,10 +5595,10 @@
         <v>76</v>
       </c>
       <c r="DP11" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="DQ11" s="8" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="DR11" s="8">
         <v>126670011</v>
@@ -5646,7 +5619,7 @@
         <v>97</v>
       </c>
       <c r="DX11" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY11" s="8" t="s">
         <v>81</v>
@@ -5667,7 +5640,7 @@
     </row>
     <row r="12" spans="1:134" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B12" s="8">
         <v>126670001</v>
@@ -5679,7 +5652,7 @@
         <v>126670092</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F12" s="8">
         <v>126670115</v>
@@ -5688,7 +5661,7 @@
         <v>965</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I12" s="8">
         <v>126670000</v>
@@ -5703,7 +5676,7 @@
         <v>73</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="N12" s="8">
         <v>0</v>
@@ -5716,17 +5689,17 @@
         <v>75000</v>
       </c>
       <c r="R12" s="8" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="S12" s="8">
         <v>90</v>
       </c>
       <c r="T12" s="8" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="U12" s="8"/>
       <c r="V12" s="8" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="W12" s="8">
         <v>126670008</v>
@@ -5747,10 +5720,10 @@
         <v>97531513</v>
       </c>
       <c r="AE12" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF12" s="8" t="s">
-        <v>231</v>
+        <v>288</v>
+      </c>
+      <c r="AF12" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AG12" s="7" t="s">
         <v>77</v>
@@ -5767,8 +5740,8 @@
       <c r="AK12" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="AL12" s="8" t="s">
-        <v>231</v>
+      <c r="AL12" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="AM12" s="7" t="s">
         <v>77</v>
@@ -5786,10 +5759,10 @@
         <v>79</v>
       </c>
       <c r="AR12" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="AS12" s="8" t="s">
-        <v>232</v>
+        <v>289</v>
+      </c>
+      <c r="AS12" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="AT12" s="7" t="s">
         <v>81</v>
@@ -5798,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="AV12" s="7" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="AW12" s="8" t="s">
         <v>83</v>
@@ -5816,7 +5789,7 @@
         <v>19312338</v>
       </c>
       <c r="BB12" s="8" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="BC12" s="8">
         <v>126670001</v>
@@ -5829,7 +5802,7 @@
         <v>126670092</v>
       </c>
       <c r="BG12" s="8" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="BH12" s="8">
         <v>126670115</v>
@@ -5838,7 +5811,7 @@
         <v>965</v>
       </c>
       <c r="BJ12" s="8" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="BK12" s="8">
         <v>126670000</v>
@@ -5847,7 +5820,7 @@
         <v>72</v>
       </c>
       <c r="BM12" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="BN12" s="8"/>
       <c r="BO12" s="8" t="s">
@@ -5861,16 +5834,16 @@
         <v>75000</v>
       </c>
       <c r="BS12" s="8" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="BT12" s="8" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="BU12" s="8"/>
       <c r="BV12" s="8"/>
       <c r="BW12" s="21"/>
       <c r="BX12" s="8" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="BY12" s="8">
         <v>126670037</v>
@@ -5883,19 +5856,19 @@
         <v>97531513</v>
       </c>
       <c r="CC12" s="8" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="CD12" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="CE12" s="8" t="s">
-        <v>231</v>
+        <v>290</v>
+      </c>
+      <c r="CE12" s="9" t="s">
+        <v>230</v>
       </c>
       <c r="CF12" s="18" t="s">
         <v>77</v>
       </c>
       <c r="CG12" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="CH12" s="8"/>
       <c r="CI12" s="8">
@@ -5920,10 +5893,10 @@
         <v>115</v>
       </c>
       <c r="CP12" s="8" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="CQ12" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="CR12" s="16" t="s">
         <v>81</v>
@@ -5950,7 +5923,7 @@
         <v>19312338</v>
       </c>
       <c r="CZ12" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="DA12" s="8">
         <v>126670001</v>
@@ -5983,13 +5956,13 @@
         <v>74</v>
       </c>
       <c r="DK12" s="8" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="DL12" s="8">
         <v>97531513</v>
       </c>
       <c r="DM12" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="DN12" s="8">
         <v>126670037</v>
@@ -5998,10 +5971,10 @@
         <v>76</v>
       </c>
       <c r="DP12" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="DQ12" s="8" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="DR12" s="8">
         <v>126670037</v>
@@ -6022,7 +5995,7 @@
         <v>116</v>
       </c>
       <c r="DX12" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="DY12" s="8" t="s">
         <v>81</v>
@@ -6042,381 +6015,144 @@
       <c r="ED12" s="8"/>
     </row>
     <row r="13" spans="1:134" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="8">
-        <v>126670000</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="8">
-        <v>126670232</v>
-      </c>
-      <c r="G13" s="8">
-        <v>44</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="I13" s="8">
-        <v>126670185</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>74</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="7"/>
       <c r="P13" s="9"/>
-      <c r="Q13" s="11">
-        <v>75000</v>
-      </c>
-      <c r="R13" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="S13" s="8">
-        <v>101</v>
-      </c>
-      <c r="T13" s="8" t="s">
-        <v>317</v>
-      </c>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
       <c r="U13" s="8"/>
-      <c r="V13" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="W13" s="8">
-        <v>126670008</v>
-      </c>
-      <c r="X13" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="7"/>
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
-      <c r="AA13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="AB13" s="7" t="s">
-        <v>76</v>
-      </c>
+      <c r="AA13" s="8"/>
+      <c r="AB13" s="7"/>
       <c r="AC13" s="8"/>
-      <c r="AD13" s="25">
-        <v>7950445830</v>
-      </c>
+      <c r="AD13" s="25"/>
       <c r="AE13" s="8"/>
-      <c r="AF13" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="AI13" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="AJ13" s="7">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL13" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="AM13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="AN13" s="8">
-        <v>1</v>
-      </c>
-      <c r="AO13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AP13" s="8">
-        <v>3</v>
-      </c>
-      <c r="AQ13" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="AR13" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="AS13" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="AT13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU13" s="7">
-        <v>1</v>
-      </c>
-      <c r="AV13" s="7" t="s">
-        <v>313</v>
-      </c>
+      <c r="AF13" s="8"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="8"/>
+      <c r="AI13" s="8"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="8"/>
+      <c r="AM13" s="7"/>
+      <c r="AN13" s="8"/>
+      <c r="AO13" s="7"/>
+      <c r="AP13" s="8"/>
+      <c r="AQ13" s="8"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="8"/>
+      <c r="AT13" s="7"/>
+      <c r="AU13" s="7"/>
+      <c r="AV13" s="7"/>
       <c r="AW13" s="8"/>
       <c r="AX13" s="8"/>
-      <c r="AY13" s="7">
-        <v>126670000</v>
-      </c>
-      <c r="AZ13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="BA13" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="BB13" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="BC13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="BD13" s="16" t="s">
-        <v>71</v>
-      </c>
+      <c r="AY13" s="7"/>
+      <c r="AZ13" s="7"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="8"/>
+      <c r="BC13" s="8"/>
+      <c r="BD13" s="16"/>
       <c r="BE13" s="9"/>
-      <c r="BF13" s="8">
-        <v>126670000</v>
-      </c>
-      <c r="BG13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="BH13" s="8">
-        <v>126670232</v>
-      </c>
-      <c r="BI13" s="8">
-        <v>44</v>
-      </c>
-      <c r="BJ13" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="BK13" s="8">
-        <v>126670185</v>
-      </c>
-      <c r="BL13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="BM13" s="10" t="s">
-        <v>322</v>
-      </c>
+      <c r="BF13" s="8"/>
+      <c r="BG13" s="8"/>
+      <c r="BH13" s="8"/>
+      <c r="BI13" s="8"/>
+      <c r="BJ13" s="8"/>
+      <c r="BK13" s="8"/>
+      <c r="BL13" s="8"/>
+      <c r="BM13" s="10"/>
       <c r="BN13" s="8"/>
-      <c r="BO13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="BP13" s="8">
-        <v>0</v>
-      </c>
+      <c r="BO13" s="8"/>
+      <c r="BP13" s="8"/>
       <c r="BQ13" s="9"/>
-      <c r="BR13" s="15">
-        <v>75000</v>
-      </c>
-      <c r="BS13" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="BT13" s="8" t="s">
-        <v>317</v>
-      </c>
+      <c r="BR13" s="15"/>
+      <c r="BS13" s="8"/>
+      <c r="BT13" s="8"/>
       <c r="BU13" s="8"/>
-      <c r="BV13" s="8">
-        <v>0</v>
-      </c>
-      <c r="BW13" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="BX13" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="BY13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="BZ13" s="16" t="s">
-        <v>76</v>
-      </c>
+      <c r="BV13" s="8"/>
+      <c r="BW13" s="16"/>
+      <c r="BX13" s="8"/>
+      <c r="BY13" s="8"/>
+      <c r="BZ13" s="16"/>
       <c r="CA13" s="8"/>
-      <c r="CB13" s="8">
-        <v>7950445830</v>
-      </c>
+      <c r="CB13" s="8"/>
       <c r="CC13" s="8"/>
-      <c r="CD13" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="CE13" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="CF13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="CG13" s="8" t="s">
-        <v>321</v>
-      </c>
+      <c r="CD13" s="8"/>
+      <c r="CE13" s="8"/>
+      <c r="CF13" s="18"/>
+      <c r="CG13" s="8"/>
       <c r="CH13" s="8"/>
-      <c r="CI13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="CJ13" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="CK13" s="8">
-        <v>0</v>
-      </c>
-      <c r="CL13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="CM13" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="CN13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="CO13" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="CP13" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="CQ13" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="CR13" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="CS13" s="16">
-        <v>1</v>
-      </c>
-      <c r="CT13" s="16" t="s">
-        <v>82</v>
-      </c>
+      <c r="CI13" s="8"/>
+      <c r="CJ13" s="8"/>
+      <c r="CK13" s="8"/>
+      <c r="CL13" s="8"/>
+      <c r="CM13" s="16"/>
+      <c r="CN13" s="8"/>
+      <c r="CO13" s="16"/>
+      <c r="CP13" s="8"/>
+      <c r="CQ13" s="8"/>
+      <c r="CR13" s="16"/>
+      <c r="CS13" s="16"/>
+      <c r="CT13" s="16"/>
       <c r="CU13" s="8"/>
       <c r="CV13" s="8"/>
-      <c r="CW13" s="7">
-        <v>126670000</v>
-      </c>
-      <c r="CX13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="CY13" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="CZ13" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="DA13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="DB13" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="DC13" s="8">
-        <v>587030004</v>
-      </c>
-      <c r="DD13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="DE13" s="8">
-        <v>126670185</v>
-      </c>
-      <c r="DF13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="DG13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="DH13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="DI13" s="8">
-        <v>0</v>
-      </c>
-      <c r="DJ13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="DK13" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="DL13" s="8">
-        <v>7950445830</v>
-      </c>
-      <c r="DM13" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="DN13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="DO13" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="DP13" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="DQ13" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="DR13" s="8">
-        <v>126670037</v>
-      </c>
-      <c r="DS13" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="DT13" s="8">
-        <v>0</v>
-      </c>
-      <c r="DU13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="DV13" s="8">
-        <v>126670000</v>
-      </c>
-      <c r="DW13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="DX13" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="DY13" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="DZ13" s="8">
-        <v>126670001</v>
-      </c>
-      <c r="EA13" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="EB13" s="8">
-        <v>126670000</v>
-      </c>
-      <c r="EC13" s="8" t="s">
-        <v>74</v>
-      </c>
+      <c r="CW13" s="7"/>
+      <c r="CX13" s="7"/>
+      <c r="CY13" s="8"/>
+      <c r="CZ13" s="8"/>
+      <c r="DA13" s="8"/>
+      <c r="DB13" s="8"/>
+      <c r="DC13" s="8"/>
+      <c r="DD13" s="8"/>
+      <c r="DE13" s="8"/>
+      <c r="DF13" s="8"/>
+      <c r="DG13" s="8"/>
+      <c r="DH13" s="8"/>
+      <c r="DI13" s="8"/>
+      <c r="DJ13" s="8"/>
+      <c r="DK13" s="8"/>
+      <c r="DL13" s="8"/>
+      <c r="DM13" s="10"/>
+      <c r="DN13" s="8"/>
+      <c r="DO13" s="8"/>
+      <c r="DP13" s="8"/>
+      <c r="DQ13" s="8"/>
+      <c r="DR13" s="8"/>
+      <c r="DS13" s="8"/>
+      <c r="DT13" s="8"/>
+      <c r="DU13" s="8"/>
+      <c r="DV13" s="8"/>
+      <c r="DW13" s="8"/>
+      <c r="DX13" s="8"/>
+      <c r="DY13" s="8"/>
+      <c r="DZ13" s="8"/>
+      <c r="EA13" s="8"/>
+      <c r="EB13" s="8"/>
+      <c r="EC13" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="BM13" r:id="rId1" xr:uid="{AAB40E64-6F1B-4B89-BA48-811BE7B1F38F}"/>
-    <hyperlink ref="M13" r:id="rId2" xr:uid="{5EB63A32-A297-499F-8141-4772E894122B}"/>
-    <hyperlink ref="DM13" r:id="rId3" xr:uid="{DD536DE6-1CAD-4016-BD04-D719C5552978}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
